--- a/artfynd/A 48855-2023 artfynd.xlsx
+++ b/artfynd/A 48855-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48855-2023 artfynd.xlsx
+++ b/artfynd/A 48855-2023 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 48855-2023 artfynd.xlsx
+++ b/artfynd/A 48855-2023 artfynd.xlsx
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112123299</v>
+        <v>112122557</v>
       </c>
       <c r="B2" t="n">
-        <v>90865</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Bjurtjärnen (Lilla Bjurtjärnen), Vrm</t>
+          <t>Lilla Bjurtjärnen, Lilla Bjurtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>358578</v>
+        <v>358536</v>
       </c>
       <c r="R2" t="n">
-        <v>6579399</v>
+        <v>6579333</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,17 +756,22 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -788,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112122557</v>
+        <v>112123299</v>
       </c>
       <c r="B3" t="n">
-        <v>89606</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +799,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Bjurtjärnen (Lilla Bjurtjärnen), Vrm</t>
+          <t>Lilla Bjurtjärnen, Lilla Bjurtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>358536</v>
+        <v>358578</v>
       </c>
       <c r="R3" t="n">
-        <v>6579334</v>
+        <v>6579399</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,7 +859,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,22 +869,17 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,12 +899,7 @@
         <v>112123380</v>
       </c>
       <c r="B4" t="n">
-        <v>89556</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,7 +928,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Bjurtjärnen (Lilla Bjurtjärnen), Vrm</t>
+          <t>Lilla Bjurtjärnen, Lilla Bjurtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 48855-2023 artfynd.xlsx
+++ b/artfynd/A 48855-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112122557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112123299</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112123380</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>